--- a/input/timetable/Режиссура театрализованных представлений, НХК. xlsx.xlsx
+++ b/input/timetable/Режиссура театрализованных представлений, НХК. xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="90">
   <si>
     <t>пара</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Иностранный язык в проф. сфере      ( пр 24 ч), п/г2, К312</t>
+  </si>
+  <si>
+    <t>Режиссура праздника под открытым небом (пр), К427</t>
   </si>
 </sst>
 </file>
@@ -1228,6 +1231,163 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1246,198 +1406,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1447,22 +1423,19 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1478,6 +1451,15 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1493,6 +1475,63 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1515,42 +1554,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1965,10 +1968,10 @@
       <c r="A7" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="69"/>
+      <c r="D7" s="107"/>
       <c r="E7" s="33" t="s">
         <v>38</v>
       </c>
@@ -1980,12 +1983,12 @@
       <c r="A8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
@@ -2008,46 +2011,46 @@
       <c r="B10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="72"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="75"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="18"/>
       <c r="B11" s="17">
         <v>4</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="114" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="81"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="116"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="18"/>
       <c r="B12" s="19">
         <v>5</v>
       </c>
-      <c r="C12" s="82" t="s">
+      <c r="C12" s="117" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83" t="s">
+      <c r="D12" s="118"/>
+      <c r="E12" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="84"/>
+      <c r="F12" s="119"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="20"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="75"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="110"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
@@ -2056,58 +2059,58 @@
       <c r="B14" s="23">
         <v>2</v>
       </c>
-      <c r="C14" s="102" t="s">
+      <c r="C14" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="104"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="63"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="18"/>
       <c r="B15" s="19">
         <v>3</v>
       </c>
-      <c r="C15" s="76" t="s">
+      <c r="C15" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="78"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="113"/>
     </row>
     <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="18"/>
       <c r="B16" s="19">
         <v>4</v>
       </c>
-      <c r="C16" s="85" t="s">
+      <c r="C16" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="87"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="66"/>
     </row>
     <row r="17" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="18"/>
       <c r="B17" s="19">
         <v>5</v>
       </c>
-      <c r="C17" s="85" t="s">
+      <c r="C17" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="87"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="66"/>
     </row>
     <row r="18" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="24"/>
       <c r="B18" s="21">
         <v>6</v>
       </c>
-      <c r="C18" s="88"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="90"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="99"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19" s="22" t="s">
@@ -2116,44 +2119,44 @@
       <c r="B19" s="23">
         <v>2</v>
       </c>
-      <c r="C19" s="91"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="92"/>
-      <c r="F19" s="93"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="102"/>
     </row>
     <row r="20" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="18"/>
       <c r="B20" s="19">
         <v>3</v>
       </c>
-      <c r="C20" s="95"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="97"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="106"/>
     </row>
     <row r="21" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="18"/>
       <c r="B21" s="19">
         <v>4</v>
       </c>
-      <c r="C21" s="85" t="s">
+      <c r="C21" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="87"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="66"/>
     </row>
     <row r="22" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="24"/>
       <c r="B22" s="21">
         <v>5</v>
       </c>
-      <c r="C22" s="108" t="s">
+      <c r="C22" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="110"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="72"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23" s="22" t="s">
@@ -2162,22 +2165,22 @@
       <c r="B23" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="70" t="s">
+      <c r="C23" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="72"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="75"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="18"/>
       <c r="B24" s="19">
         <v>4</v>
       </c>
-      <c r="C24" s="123"/>
-      <c r="D24" s="124"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="125"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="90"/>
       <c r="P24" s="56"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -2185,18 +2188,18 @@
       <c r="B25" s="19">
         <v>5</v>
       </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="59"/>
+      <c r="C25" s="120"/>
+      <c r="D25" s="121"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="122"/>
     </row>
     <row r="26" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="25"/>
       <c r="B26" s="26"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="119"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="84"/>
     </row>
     <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="22" t="s">
@@ -2205,46 +2208,46 @@
       <c r="B27" s="23">
         <v>3</v>
       </c>
-      <c r="C27" s="120"/>
-      <c r="D27" s="121"/>
-      <c r="E27" s="121"/>
-      <c r="F27" s="122"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="87"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="27"/>
       <c r="B28" s="19">
         <v>4</v>
       </c>
-      <c r="C28" s="105" t="s">
+      <c r="C28" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="107"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="69"/>
     </row>
     <row r="29" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="38"/>
       <c r="B29" s="26">
         <v>5</v>
       </c>
-      <c r="C29" s="129" t="s">
+      <c r="C29" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="130"/>
-      <c r="E29" s="130"/>
-      <c r="F29" s="131"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="96"/>
     </row>
     <row r="30" spans="1:16" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="28"/>
       <c r="B30" s="26">
         <v>6</v>
       </c>
-      <c r="C30" s="126" t="s">
+      <c r="C30" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="127"/>
-      <c r="E30" s="127"/>
-      <c r="F30" s="128"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="93"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31" s="39" t="s">
@@ -2253,104 +2256,104 @@
       <c r="B31" s="23">
         <v>2</v>
       </c>
-      <c r="C31" s="60" t="s">
+      <c r="C31" s="123" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="62"/>
+      <c r="D31" s="124"/>
+      <c r="E31" s="124"/>
+      <c r="F31" s="125"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32" s="40"/>
       <c r="B32" s="19">
         <v>3</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="67"/>
-      <c r="E32" s="67"/>
-      <c r="F32" s="68"/>
+      <c r="D32" s="130"/>
+      <c r="E32" s="130"/>
+      <c r="F32" s="131"/>
     </row>
     <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="40"/>
       <c r="B33" s="19">
         <v>4</v>
       </c>
-      <c r="C33" s="66" t="s">
+      <c r="C33" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="67"/>
-      <c r="E33" s="67"/>
-      <c r="F33" s="68"/>
+      <c r="D33" s="130"/>
+      <c r="E33" s="130"/>
+      <c r="F33" s="131"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="41"/>
       <c r="B34" s="21">
         <v>5</v>
       </c>
-      <c r="C34" s="63" t="s">
+      <c r="C34" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="65"/>
+      <c r="D34" s="127"/>
+      <c r="E34" s="127"/>
+      <c r="F34" s="128"/>
     </row>
     <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="42"/>
       <c r="B35" s="43"/>
-      <c r="C35" s="111"/>
-      <c r="D35" s="112"/>
-      <c r="E35" s="112"/>
-      <c r="F35" s="113"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="78"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="52"/>
       <c r="B36" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="99" t="s">
+      <c r="C36" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="D36" s="100"/>
-      <c r="E36" s="100"/>
-      <c r="F36" s="101"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="60"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="40"/>
       <c r="B37" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="105" t="s">
+      <c r="C37" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="106"/>
-      <c r="E37" s="106"/>
-      <c r="F37" s="107"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="69"/>
     </row>
     <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="41"/>
       <c r="B38" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="114" t="s">
+      <c r="C38" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="115"/>
-      <c r="E38" s="115"/>
-      <c r="F38" s="116"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="81"/>
     </row>
     <row r="39" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="50" t="s">
         <v>40</v>
       </c>
       <c r="B39" s="51"/>
-      <c r="C39" s="98" t="s">
+      <c r="C39" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="D39" s="98"/>
-      <c r="E39" s="98"/>
-      <c r="F39" s="98"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B40" s="1" t="s">
@@ -2370,6 +2373,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C20:F20"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C14:F14"/>
@@ -2386,23 +2406,6 @@
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -2515,10 +2518,10 @@
       <c r="A7" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="69"/>
+      <c r="D7" s="107"/>
       <c r="E7" s="33" t="s">
         <v>64</v>
       </c>
@@ -2530,12 +2533,12 @@
       <c r="A8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
@@ -2558,46 +2561,46 @@
       <c r="B10" s="17">
         <v>1</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="72"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="75"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="18"/>
       <c r="B11" s="19">
         <v>2</v>
       </c>
-      <c r="C11" s="135" t="s">
+      <c r="C11" s="141" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="137"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="143"/>
     </row>
     <row r="12" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="18"/>
       <c r="B12" s="19">
         <v>3</v>
       </c>
-      <c r="C12" s="76"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77" t="s">
+      <c r="C12" s="111"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="F12" s="78"/>
+      <c r="F12" s="113"/>
     </row>
     <row r="13" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="20"/>
       <c r="B13" s="21">
         <v>4</v>
       </c>
-      <c r="C13" s="138"/>
-      <c r="D13" s="139"/>
-      <c r="E13" s="139"/>
-      <c r="F13" s="140"/>
+      <c r="C13" s="171"/>
+      <c r="D13" s="172"/>
+      <c r="E13" s="172"/>
+      <c r="F13" s="173"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
@@ -2606,48 +2609,48 @@
       <c r="B14" s="23">
         <v>1</v>
       </c>
-      <c r="C14" s="132" t="s">
+      <c r="C14" s="168" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="133"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="134"/>
+      <c r="D14" s="169"/>
+      <c r="E14" s="169"/>
+      <c r="F14" s="170"/>
     </row>
     <row r="15" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="18"/>
       <c r="B15" s="19">
         <v>2</v>
       </c>
-      <c r="C15" s="141" t="s">
+      <c r="C15" s="153" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="143"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="155"/>
     </row>
     <row r="16" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="18"/>
       <c r="B16" s="19">
         <v>3</v>
       </c>
-      <c r="C16" s="144" t="s">
+      <c r="C16" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="145"/>
-      <c r="E16" s="145"/>
-      <c r="F16" s="146"/>
+      <c r="D16" s="136"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="137"/>
     </row>
     <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="24"/>
       <c r="B17" s="21">
         <v>4</v>
       </c>
-      <c r="C17" s="144" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="145"/>
-      <c r="E17" s="145"/>
-      <c r="F17" s="146"/>
+      <c r="C17" s="135" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="137"/>
     </row>
     <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="22" t="s">
@@ -2656,46 +2659,46 @@
       <c r="B18" s="23">
         <v>1</v>
       </c>
-      <c r="C18" s="147"/>
-      <c r="D18" s="148"/>
-      <c r="E18" s="148"/>
-      <c r="F18" s="149"/>
+      <c r="C18" s="165"/>
+      <c r="D18" s="166"/>
+      <c r="E18" s="166"/>
+      <c r="F18" s="167"/>
     </row>
     <row r="19" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="18"/>
       <c r="B19" s="19">
         <v>2</v>
       </c>
-      <c r="C19" s="76" t="s">
+      <c r="C19" s="111" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="78"/>
+      <c r="D19" s="112"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="113"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="18"/>
       <c r="B20" s="19">
         <v>3</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="111" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="78"/>
+      <c r="D20" s="112"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="113"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="24"/>
       <c r="B21" s="21">
         <v>4</v>
       </c>
-      <c r="C21" s="150" t="s">
+      <c r="C21" s="132" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="151"/>
-      <c r="E21" s="151"/>
-      <c r="F21" s="152"/>
+      <c r="D21" s="133"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="134"/>
     </row>
     <row r="22" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="22" t="s">
@@ -2704,46 +2707,46 @@
       <c r="B22" s="23">
         <v>1</v>
       </c>
-      <c r="C22" s="99" t="s">
+      <c r="C22" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="171"/>
-      <c r="E22" s="172"/>
-      <c r="F22" s="173"/>
+      <c r="D22" s="162"/>
+      <c r="E22" s="163"/>
+      <c r="F22" s="164"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="18"/>
       <c r="B23" s="19">
         <v>2</v>
       </c>
-      <c r="C23" s="144" t="s">
+      <c r="C23" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="145"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="146"/>
+      <c r="D23" s="136"/>
+      <c r="E23" s="136"/>
+      <c r="F23" s="137"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="25"/>
       <c r="B24" s="26">
         <v>3</v>
       </c>
-      <c r="C24" s="144" t="s">
+      <c r="C24" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="145"/>
-      <c r="E24" s="145"/>
-      <c r="F24" s="146"/>
+      <c r="D24" s="136"/>
+      <c r="E24" s="136"/>
+      <c r="F24" s="137"/>
     </row>
     <row r="25" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="24"/>
       <c r="B25" s="21">
         <v>4</v>
       </c>
-      <c r="C25" s="159"/>
-      <c r="D25" s="160"/>
-      <c r="E25" s="160"/>
-      <c r="F25" s="161"/>
+      <c r="C25" s="147"/>
+      <c r="D25" s="148"/>
+      <c r="E25" s="148"/>
+      <c r="F25" s="149"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="22" t="s">
@@ -2752,44 +2755,44 @@
       <c r="B26" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="162" t="s">
+      <c r="C26" s="150" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="163"/>
-      <c r="E26" s="163"/>
-      <c r="F26" s="164"/>
+      <c r="D26" s="151"/>
+      <c r="E26" s="151"/>
+      <c r="F26" s="152"/>
     </row>
     <row r="27" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="27"/>
       <c r="B27" s="19">
         <v>4</v>
       </c>
-      <c r="C27" s="141" t="s">
+      <c r="C27" s="153" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="142"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="143"/>
+      <c r="D27" s="154"/>
+      <c r="E27" s="154"/>
+      <c r="F27" s="155"/>
     </row>
     <row r="28" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="27"/>
       <c r="B28" s="19">
         <v>5</v>
       </c>
-      <c r="C28" s="141" t="s">
+      <c r="C28" s="153" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="142"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="143"/>
+      <c r="D28" s="154"/>
+      <c r="E28" s="154"/>
+      <c r="F28" s="155"/>
     </row>
     <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="28"/>
       <c r="B29" s="21"/>
-      <c r="C29" s="165"/>
-      <c r="D29" s="166"/>
-      <c r="E29" s="166"/>
-      <c r="F29" s="167"/>
+      <c r="C29" s="156"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="157"/>
+      <c r="F29" s="158"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="29" t="s">
@@ -2798,58 +2801,58 @@
       <c r="B30" s="17">
         <v>1</v>
       </c>
-      <c r="C30" s="168"/>
-      <c r="D30" s="169"/>
-      <c r="E30" s="169"/>
-      <c r="F30" s="170"/>
+      <c r="C30" s="159"/>
+      <c r="D30" s="160"/>
+      <c r="E30" s="160"/>
+      <c r="F30" s="161"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="30"/>
       <c r="B31" s="19">
         <v>2</v>
       </c>
-      <c r="C31" s="153" t="s">
+      <c r="C31" s="138" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="154"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="155"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="140"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="30"/>
       <c r="B32" s="19">
         <v>3</v>
       </c>
-      <c r="C32" s="135" t="s">
+      <c r="C32" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="136"/>
-      <c r="E32" s="136"/>
-      <c r="F32" s="137"/>
+      <c r="D32" s="142"/>
+      <c r="E32" s="142"/>
+      <c r="F32" s="143"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="31"/>
       <c r="B33" s="45">
         <v>4</v>
       </c>
-      <c r="C33" s="156" t="s">
+      <c r="C33" s="144" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="157"/>
-      <c r="E33" s="157"/>
-      <c r="F33" s="158"/>
+      <c r="D33" s="145"/>
+      <c r="E33" s="145"/>
+      <c r="F33" s="146"/>
     </row>
     <row r="34" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="50" t="s">
         <v>40</v>
       </c>
       <c r="B34" s="51"/>
-      <c r="C34" s="98" t="s">
+      <c r="C34" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
@@ -2869,6 +2872,20 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C18:F18"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C24:F24"/>
@@ -2884,20 +2901,6 @@
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3010,10 +3013,10 @@
       <c r="A7" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="69"/>
+      <c r="D7" s="107"/>
       <c r="E7" s="33" t="s">
         <v>77</v>
       </c>
@@ -3035,11 +3038,11 @@
       <c r="A9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="94" t="s">
+      <c r="C9" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103"/>
     </row>
     <row r="10" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="14" t="s">
@@ -3062,12 +3065,12 @@
       <c r="B11" s="17">
         <v>3</v>
       </c>
-      <c r="C11" s="147" t="s">
+      <c r="C11" s="165" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="148"/>
-      <c r="E11" s="148"/>
-      <c r="F11" s="149"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="167"/>
       <c r="L11" s="56"/>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -3075,36 +3078,36 @@
       <c r="B12" s="19">
         <v>4</v>
       </c>
-      <c r="C12" s="105" t="s">
+      <c r="C12" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="106"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="107"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="69"/>
     </row>
     <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="18"/>
       <c r="B13" s="19">
         <v>5</v>
       </c>
-      <c r="C13" s="105" t="s">
+      <c r="C13" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="107"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="69"/>
     </row>
     <row r="14" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="18"/>
       <c r="B14" s="19">
         <v>6</v>
       </c>
-      <c r="C14" s="186" t="s">
+      <c r="C14" s="180" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="187"/>
-      <c r="E14" s="187"/>
-      <c r="F14" s="188"/>
+      <c r="D14" s="181"/>
+      <c r="E14" s="181"/>
+      <c r="F14" s="182"/>
     </row>
     <row r="15" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
@@ -3113,46 +3116,46 @@
       <c r="B15" s="23">
         <v>2</v>
       </c>
-      <c r="C15" s="189" t="s">
+      <c r="C15" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="190"/>
-      <c r="E15" s="190"/>
-      <c r="F15" s="191"/>
+      <c r="D15" s="184"/>
+      <c r="E15" s="184"/>
+      <c r="F15" s="185"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="18"/>
       <c r="B16" s="19">
         <v>3</v>
       </c>
-      <c r="C16" s="105" t="s">
+      <c r="C16" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="107"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="69"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="18"/>
       <c r="B17" s="19">
         <v>4</v>
       </c>
-      <c r="C17" s="135" t="s">
+      <c r="C17" s="141" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="137"/>
+      <c r="D17" s="142"/>
+      <c r="E17" s="142"/>
+      <c r="F17" s="143"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="25"/>
       <c r="B18" s="26">
         <v>5</v>
       </c>
-      <c r="C18" s="85"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="87"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="66"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="22" t="s">
@@ -3161,48 +3164,48 @@
       <c r="B19" s="23">
         <v>3</v>
       </c>
-      <c r="C19" s="99" t="s">
+      <c r="C19" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="100"/>
-      <c r="E19" s="100"/>
-      <c r="F19" s="101"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="60"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="18"/>
       <c r="B20" s="19">
         <v>4</v>
       </c>
-      <c r="C20" s="105" t="s">
+      <c r="C20" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="107"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="69"/>
     </row>
     <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="18"/>
       <c r="B21" s="19">
         <v>5</v>
       </c>
-      <c r="C21" s="105" t="s">
+      <c r="C21" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="107"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="69"/>
     </row>
     <row r="22" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="24"/>
       <c r="B22" s="21">
         <v>6</v>
       </c>
-      <c r="C22" s="85" t="s">
+      <c r="C22" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="87"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="66"/>
     </row>
     <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="22" t="s">
@@ -3211,48 +3214,48 @@
       <c r="B23" s="23">
         <v>2</v>
       </c>
-      <c r="C23" s="195" t="s">
+      <c r="C23" s="177" t="s">
         <v>83</v>
       </c>
-      <c r="D23" s="196"/>
-      <c r="E23" s="196"/>
-      <c r="F23" s="197"/>
+      <c r="D23" s="178"/>
+      <c r="E23" s="178"/>
+      <c r="F23" s="179"/>
     </row>
     <row r="24" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="18"/>
       <c r="B24" s="19">
         <v>3</v>
       </c>
-      <c r="C24" s="135" t="s">
+      <c r="C24" s="141" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="136"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="137"/>
+      <c r="D24" s="142"/>
+      <c r="E24" s="142"/>
+      <c r="F24" s="143"/>
     </row>
     <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="18"/>
       <c r="B25" s="19">
         <v>4</v>
       </c>
-      <c r="C25" s="135" t="s">
+      <c r="C25" s="141" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="136"/>
-      <c r="E25" s="136"/>
-      <c r="F25" s="137"/>
+      <c r="D25" s="142"/>
+      <c r="E25" s="142"/>
+      <c r="F25" s="143"/>
     </row>
     <row r="26" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="24"/>
       <c r="B26" s="21">
         <v>5</v>
       </c>
-      <c r="C26" s="192" t="s">
+      <c r="C26" s="174" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="193"/>
-      <c r="E26" s="193"/>
-      <c r="F26" s="194"/>
+      <c r="D26" s="175"/>
+      <c r="E26" s="175"/>
+      <c r="F26" s="176"/>
     </row>
     <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="22" t="s">
@@ -3261,44 +3264,44 @@
       <c r="B27" s="23">
         <v>2</v>
       </c>
-      <c r="C27" s="60" t="s">
+      <c r="C27" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="61"/>
-      <c r="E27" s="61"/>
-      <c r="F27" s="62"/>
+      <c r="D27" s="124"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="125"/>
     </row>
     <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="27"/>
       <c r="B28" s="19">
         <v>3</v>
       </c>
-      <c r="C28" s="135" t="s">
+      <c r="C28" s="141" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="136"/>
-      <c r="E28" s="136"/>
-      <c r="F28" s="137"/>
+      <c r="D28" s="142"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="143"/>
     </row>
     <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="27"/>
       <c r="B29" s="19">
         <v>4</v>
       </c>
-      <c r="C29" s="183"/>
-      <c r="D29" s="184"/>
-      <c r="E29" s="184"/>
-      <c r="F29" s="185"/>
+      <c r="C29" s="195"/>
+      <c r="D29" s="196"/>
+      <c r="E29" s="196"/>
+      <c r="F29" s="197"/>
     </row>
     <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="28"/>
       <c r="B30" s="21">
         <v>5</v>
       </c>
-      <c r="C30" s="180"/>
-      <c r="D30" s="181"/>
-      <c r="E30" s="181"/>
-      <c r="F30" s="182"/>
+      <c r="C30" s="192"/>
+      <c r="D30" s="193"/>
+      <c r="E30" s="193"/>
+      <c r="F30" s="194"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="29" t="s">
@@ -3307,32 +3310,32 @@
       <c r="B31" s="17">
         <v>1</v>
       </c>
-      <c r="C31" s="174" t="s">
+      <c r="C31" s="186" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="175"/>
-      <c r="E31" s="175"/>
-      <c r="F31" s="176"/>
+      <c r="D31" s="187"/>
+      <c r="E31" s="187"/>
+      <c r="F31" s="188"/>
     </row>
     <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="30"/>
       <c r="B32" s="19">
         <v>2</v>
       </c>
-      <c r="C32" s="105"/>
-      <c r="D32" s="106"/>
-      <c r="E32" s="106"/>
-      <c r="F32" s="107"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="69"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="31"/>
       <c r="B33" s="45">
         <v>3</v>
       </c>
-      <c r="C33" s="177"/>
-      <c r="D33" s="178"/>
-      <c r="E33" s="178"/>
-      <c r="F33" s="179"/>
+      <c r="C33" s="189"/>
+      <c r="D33" s="190"/>
+      <c r="E33" s="190"/>
+      <c r="F33" s="191"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="46"/>
@@ -3360,6 +3363,22 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C26:F26"/>
@@ -3369,22 +3388,6 @@
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>

--- a/input/timetable/Режиссура театрализованных представлений, НХК. xlsx.xlsx
+++ b/input/timetable/Режиссура театрализованных представлений, НХК. xlsx.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13305" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13305" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2 курс" sheetId="26" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="107">
   <si>
     <t>пара</t>
   </si>
@@ -76,6 +76,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -118,18 +121,36 @@
     <t>ТО</t>
   </si>
   <si>
+    <t>Шевкунов А.Н.</t>
+  </si>
+  <si>
+    <t>Бирюкова Н.С.</t>
+  </si>
+  <si>
+    <t>Куляшова М.А.</t>
+  </si>
+  <si>
     <t>Режиссура (пр), К420</t>
   </si>
   <si>
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
+    <t>Бедных О.Г.</t>
+  </si>
+  <si>
+    <t>Забирова В.Х.</t>
+  </si>
+  <si>
     <t>Музыкальное оформление проекта (лек), К420</t>
   </si>
   <si>
     <t>51.03.05 Режиссура театрализованных представлений и праздников</t>
   </si>
   <si>
+    <t>Раздобреев О.В.</t>
+  </si>
+  <si>
     <t>Иностранный язык в проф. сфере ( пр 24 ч), п/г1, К407</t>
   </si>
   <si>
@@ -154,6 +175,9 @@
     <t>Философия (лек 32 ч)</t>
   </si>
   <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
@@ -217,15 +241,33 @@
     <t>02.02.2026-08.04.2026</t>
   </si>
   <si>
+    <t>Царская Т.С.; Савш И.Ю.</t>
+  </si>
+  <si>
+    <t>Куляшова М.А./Раздобреев О.В.</t>
+  </si>
+  <si>
+    <t>Кутьков И.Р.</t>
+  </si>
+  <si>
     <t>210-31</t>
   </si>
   <si>
+    <t>Апокин В.В.</t>
+  </si>
+  <si>
     <t>Музыкальное оформление проекта (пр), К420//</t>
   </si>
   <si>
     <t>Режиссура праздника под открытым небом (пр), К420</t>
   </si>
   <si>
+    <t>Шевкунов А.Н./Раздобреев О.В.</t>
+  </si>
+  <si>
+    <t>Замятина М.С.</t>
+  </si>
+  <si>
     <t>//Работа в команде (пр), К429</t>
   </si>
   <si>
@@ -241,6 +283,9 @@
     <t>Элективные дисциплины по физической культуре и спорту проводятся  1 парой или  2 парой в зависимости от выбранной элективной дисциплины</t>
   </si>
   <si>
+    <t>Быкова Л.В.</t>
+  </si>
+  <si>
     <t>Информационно-коммуникационные технологии в сфере культуры и искусства (пр), К420//</t>
   </si>
   <si>
@@ -250,6 +295,9 @@
     <t>Информационно-коммуникационные технологии в сфере культуры и искусства (лек), К420// /Учебная практика, творческая практика (проектная практика), К420</t>
   </si>
   <si>
+    <t>Раздобреев О.В./Куляшова М.А.</t>
+  </si>
+  <si>
     <t>Методика преподавания специальных дисциплин (лек),  м/з, К420</t>
   </si>
   <si>
@@ -287,6 +335,9 @@
   </si>
   <si>
     <t>День самостоятельной работы</t>
+  </si>
+  <si>
+    <t>Калинина Е.А.</t>
   </si>
   <si>
     <t>Иностранный язык в проф. сфере      ( пр 24 ч), п/г2, К312</t>
@@ -404,7 +455,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -423,12 +474,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -545,6 +602,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -769,6 +839,19 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1083,7 +1166,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1116,16 +1199,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1149,53 +1235,55 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1212,17 +1300,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1230,24 +1316,89 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1255,65 +1406,87 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1321,239 +1494,169 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1885,7 +1988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" customWidth="1"/>
@@ -1894,11 +1997,12 @@
     <col min="4" max="4" width="17.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="18.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="18.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -1906,15 +2010,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -1922,7 +2026,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
@@ -1931,32 +2035,32 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="32"/>
+      <c r="C6" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="35"/>
       <c r="E6" s="10">
         <v>2</v>
       </c>
@@ -1964,398 +2068,467 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="107" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="107"/>
-      <c r="E7" s="33" t="s">
-        <v>38</v>
+    <row r="7" spans="1:7" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="87"/>
+      <c r="E7" s="36" t="s">
+        <v>45</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="103" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="112" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="37"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="17" t="s">
+      <c r="D9" s="38"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="88" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="64"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="19"/>
+      <c r="B11" s="18">
+        <v>4</v>
+      </c>
+      <c r="C11" s="97" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="73" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="19"/>
+      <c r="B12" s="20">
+        <v>5</v>
+      </c>
+      <c r="C12" s="100" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="102"/>
+      <c r="G12" s="65" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="21"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="92"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="53"/>
+    </row>
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="24">
+        <v>2</v>
+      </c>
+      <c r="C14" s="120" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="121"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="71" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="19"/>
+      <c r="B15" s="20">
+        <v>3</v>
+      </c>
+      <c r="C15" s="94" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="65" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="19"/>
+      <c r="B16" s="20">
+        <v>4</v>
+      </c>
+      <c r="C16" s="103" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="104"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="65" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="19"/>
+      <c r="B17" s="20">
+        <v>5</v>
+      </c>
+      <c r="C17" s="103" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="65" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="25"/>
+      <c r="B18" s="22">
+        <v>6</v>
+      </c>
+      <c r="C18" s="106"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="62"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A19" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="24">
+        <v>2</v>
+      </c>
+      <c r="C19" s="109"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="64"/>
+    </row>
+    <row r="20" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="19"/>
+      <c r="B20" s="20">
+        <v>3</v>
+      </c>
+      <c r="C20" s="113"/>
+      <c r="D20" s="114"/>
+      <c r="E20" s="114"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="53"/>
+    </row>
+    <row r="21" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="19"/>
+      <c r="B21" s="20">
+        <v>4</v>
+      </c>
+      <c r="C21" s="103" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="65" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="25"/>
+      <c r="B22" s="22">
+        <v>5</v>
+      </c>
+      <c r="C22" s="126" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="127"/>
+      <c r="E22" s="127"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="68" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A23" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="88" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="64"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="19"/>
+      <c r="B24" s="20">
+        <v>4</v>
+      </c>
+      <c r="C24" s="141"/>
+      <c r="D24" s="142"/>
+      <c r="E24" s="142"/>
+      <c r="F24" s="143"/>
+      <c r="G24" s="65"/>
+      <c r="Q24" s="60"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="19"/>
+      <c r="B25" s="20">
+        <v>5</v>
+      </c>
+      <c r="C25" s="75"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="65"/>
+    </row>
+    <row r="26" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="135"/>
+      <c r="D26" s="136"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="137"/>
+      <c r="G26" s="62"/>
+    </row>
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="24">
+        <v>3</v>
+      </c>
+      <c r="C27" s="138"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="29"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="30"/>
+      <c r="B28" s="20">
+        <v>4</v>
+      </c>
+      <c r="C28" s="123" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="124"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="66" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="41"/>
+      <c r="B29" s="27">
+        <v>5</v>
+      </c>
+      <c r="C29" s="147" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="148"/>
+      <c r="E29" s="148"/>
+      <c r="F29" s="149"/>
+      <c r="G29" s="66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="31"/>
+      <c r="B30" s="27">
+        <v>6</v>
+      </c>
+      <c r="C30" s="144" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="145"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="146"/>
+      <c r="G30" s="67" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A31" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="24">
+        <v>2</v>
+      </c>
+      <c r="C31" s="78" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="79"/>
+      <c r="E31" s="79"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="69" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A32" s="43"/>
+      <c r="B32" s="20">
+        <v>3</v>
+      </c>
+      <c r="C32" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="85"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="86"/>
+      <c r="G32" s="66" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="43"/>
+      <c r="B33" s="20">
+        <v>4</v>
+      </c>
+      <c r="C33" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="66" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="44"/>
+      <c r="B34" s="22">
+        <v>5</v>
+      </c>
+      <c r="C34" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="82"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="70" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="45"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="129"/>
+      <c r="D35" s="130"/>
+      <c r="E35" s="130"/>
+      <c r="F35" s="131"/>
+      <c r="G35" s="61"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="56"/>
+      <c r="B36" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="117" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" s="118"/>
+      <c r="E36" s="118"/>
+      <c r="F36" s="119"/>
+      <c r="G36" s="69" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="43"/>
+      <c r="B37" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="123" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="124"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="125"/>
+      <c r="G37" s="66" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="44"/>
+      <c r="B38" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="132" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" s="133"/>
+      <c r="E38" s="133"/>
+      <c r="F38" s="134"/>
+      <c r="G38" s="70" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="73" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="75"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="18"/>
-      <c r="B11" s="17">
-        <v>4</v>
-      </c>
-      <c r="C11" s="114" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="115"/>
-      <c r="E11" s="115"/>
-      <c r="F11" s="116"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19">
-        <v>5</v>
-      </c>
-      <c r="C12" s="117" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" s="118"/>
-      <c r="E12" s="118" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="119"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="110"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="23">
-        <v>2</v>
-      </c>
-      <c r="C14" s="61" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="63"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19">
-        <v>3</v>
-      </c>
-      <c r="C15" s="111" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="112"/>
-      <c r="E15" s="112"/>
-      <c r="F15" s="113"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19">
-        <v>4</v>
-      </c>
-      <c r="C16" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="66"/>
-    </row>
-    <row r="17" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19">
-        <v>5</v>
-      </c>
-      <c r="C17" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="66"/>
-    </row>
-    <row r="18" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="24"/>
-      <c r="B18" s="21">
-        <v>6</v>
-      </c>
-      <c r="C18" s="97"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="99"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A19" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="23">
-        <v>2</v>
-      </c>
-      <c r="C19" s="100"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="102"/>
-    </row>
-    <row r="20" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19">
-        <v>3</v>
-      </c>
-      <c r="C20" s="104"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="106"/>
-    </row>
-    <row r="21" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19">
-        <v>4</v>
-      </c>
-      <c r="C21" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="66"/>
-    </row>
-    <row r="22" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="24"/>
-      <c r="B22" s="21">
-        <v>5</v>
-      </c>
-      <c r="C22" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="72"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A23" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="73" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="75"/>
-    </row>
-    <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19">
-        <v>4</v>
-      </c>
-      <c r="C24" s="88"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="90"/>
-      <c r="P24" s="56"/>
-    </row>
-    <row r="25" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19">
-        <v>5</v>
-      </c>
-      <c r="C25" s="120"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="121"/>
-      <c r="F25" s="122"/>
-    </row>
-    <row r="26" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="84"/>
-    </row>
-    <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="23">
-        <v>3</v>
-      </c>
-      <c r="C27" s="85"/>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="87"/>
-    </row>
-    <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="27"/>
-      <c r="B28" s="19">
-        <v>4</v>
-      </c>
-      <c r="C28" s="67" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="69"/>
-    </row>
-    <row r="29" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="38"/>
-      <c r="B29" s="26">
-        <v>5</v>
-      </c>
-      <c r="C29" s="94" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="95"/>
-      <c r="E29" s="95"/>
-      <c r="F29" s="96"/>
-    </row>
-    <row r="30" spans="1:16" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="28"/>
-      <c r="B30" s="26">
-        <v>6</v>
-      </c>
-      <c r="C30" s="91" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="93"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A31" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="23">
-        <v>2</v>
-      </c>
-      <c r="C31" s="123" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="124"/>
-      <c r="E31" s="124"/>
-      <c r="F31" s="125"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A32" s="40"/>
-      <c r="B32" s="19">
-        <v>3</v>
-      </c>
-      <c r="C32" s="129" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="130"/>
-      <c r="E32" s="130"/>
-      <c r="F32" s="131"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="40"/>
-      <c r="B33" s="19">
-        <v>4</v>
-      </c>
-      <c r="C33" s="129" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="130"/>
-      <c r="E33" s="130"/>
-      <c r="F33" s="131"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="41"/>
-      <c r="B34" s="21">
-        <v>5</v>
-      </c>
-      <c r="C34" s="126" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="127"/>
-      <c r="E34" s="127"/>
-      <c r="F34" s="128"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="42"/>
-      <c r="B35" s="43"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="78"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="52"/>
-      <c r="B36" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="60"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="40"/>
-      <c r="B37" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="69"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="41"/>
-      <c r="B38" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="79" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
-      <c r="F38" s="81"/>
-    </row>
-    <row r="39" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="51"/>
-      <c r="C39" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B39" s="55"/>
+      <c r="C39" s="116" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="116"/>
+      <c r="E39" s="116"/>
+      <c r="F39" s="116"/>
+      <c r="G39" s="52"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B40" s="1" t="s">
         <v>15</v>
       </c>
@@ -2363,7 +2536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B41" s="1" t="s">
         <v>16</v>
       </c>
@@ -2373,23 +2546,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C20:F20"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C14:F14"/>
@@ -2406,6 +2562,23 @@
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -2436,7 +2609,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" customWidth="1"/>
@@ -2445,10 +2618,11 @@
     <col min="4" max="4" width="19.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="18.140625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -2456,15 +2630,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -2472,7 +2646,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
@@ -2481,32 +2655,32 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="32"/>
+      <c r="C6" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="35"/>
       <c r="E6" s="10">
         <v>3</v>
       </c>
@@ -2514,347 +2688,411 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="107" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="107"/>
-      <c r="E7" s="33" t="s">
-        <v>64</v>
+    <row r="7" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="87"/>
+      <c r="E7" s="36" t="s">
+        <v>75</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="103" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="112" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="37"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="17">
+      <c r="D9" s="38"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="18">
         <v>1</v>
       </c>
-      <c r="C10" s="73" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="75"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19">
+      <c r="C10" s="88" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="71" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="19"/>
+      <c r="B11" s="20">
         <v>2</v>
       </c>
-      <c r="C11" s="141" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="142"/>
-      <c r="E11" s="142"/>
-      <c r="F11" s="143"/>
-    </row>
-    <row r="12" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19">
+      <c r="C11" s="153" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="154"/>
+      <c r="E11" s="154"/>
+      <c r="F11" s="155"/>
+      <c r="G11" s="65" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="19"/>
+      <c r="B12" s="20">
         <v>3</v>
       </c>
-      <c r="C12" s="111"/>
-      <c r="D12" s="112"/>
-      <c r="E12" s="112" t="s">
+      <c r="C12" s="94"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" s="96"/>
+      <c r="G12" s="65" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="21"/>
+      <c r="B13" s="22">
+        <v>4</v>
+      </c>
+      <c r="C13" s="156"/>
+      <c r="D13" s="157"/>
+      <c r="E13" s="157"/>
+      <c r="F13" s="158"/>
+      <c r="G13" s="68"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="24">
+        <v>1</v>
+      </c>
+      <c r="C14" s="150" t="s">
         <v>88</v>
       </c>
-      <c r="F12" s="113"/>
-    </row>
-    <row r="13" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21">
+      <c r="D14" s="151"/>
+      <c r="E14" s="151"/>
+      <c r="F14" s="152"/>
+      <c r="G14" s="65" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="19"/>
+      <c r="B15" s="20">
+        <v>2</v>
+      </c>
+      <c r="C15" s="159" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="160"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="161"/>
+      <c r="G15" s="65" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="19"/>
+      <c r="B16" s="20">
+        <v>3</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="163"/>
+      <c r="E16" s="163"/>
+      <c r="F16" s="164"/>
+      <c r="G16" s="65" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="25"/>
+      <c r="B17" s="22">
         <v>4</v>
       </c>
-      <c r="C13" s="171"/>
-      <c r="D13" s="172"/>
-      <c r="E13" s="172"/>
-      <c r="F13" s="173"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="23">
-        <v>1</v>
-      </c>
-      <c r="C14" s="168" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="169"/>
-      <c r="E14" s="169"/>
-      <c r="F14" s="170"/>
-    </row>
-    <row r="15" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19">
-        <v>2</v>
-      </c>
-      <c r="C15" s="153" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
-      <c r="F15" s="155"/>
-    </row>
-    <row r="16" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19">
-        <v>3</v>
-      </c>
-      <c r="C16" s="135" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="136"/>
-      <c r="E16" s="136"/>
-      <c r="F16" s="137"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="24"/>
-      <c r="B17" s="21">
-        <v>4</v>
-      </c>
-      <c r="C17" s="135" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="136"/>
-      <c r="E17" s="136"/>
-      <c r="F17" s="137"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="23">
+      <c r="C17" s="162" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="163"/>
+      <c r="E17" s="163"/>
+      <c r="F17" s="164"/>
+      <c r="G17" s="65" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="24">
         <v>1</v>
       </c>
       <c r="C18" s="165"/>
       <c r="D18" s="166"/>
       <c r="E18" s="166"/>
       <c r="F18" s="167"/>
-    </row>
-    <row r="19" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19">
+      <c r="G18" s="71"/>
+    </row>
+    <row r="19" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="19"/>
+      <c r="B19" s="20">
         <v>2</v>
       </c>
-      <c r="C19" s="111" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="112"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="113"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19">
+      <c r="C19" s="94" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="96"/>
+      <c r="G19" s="65" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="19"/>
+      <c r="B20" s="20">
         <v>3</v>
       </c>
-      <c r="C20" s="111" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="112"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="113"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="24"/>
-      <c r="B21" s="21">
+      <c r="C20" s="94" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="65" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="25"/>
+      <c r="B21" s="22">
         <v>4</v>
       </c>
-      <c r="C21" s="132" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="133"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="134"/>
-    </row>
-    <row r="22" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="23">
+      <c r="C21" s="168" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="169"/>
+      <c r="E21" s="169"/>
+      <c r="F21" s="170"/>
+      <c r="G21" s="65" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="24">
         <v>1</v>
       </c>
-      <c r="C22" s="58" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="162"/>
-      <c r="E22" s="163"/>
-      <c r="F22" s="164"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19">
+      <c r="C22" s="117" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="189"/>
+      <c r="E22" s="190"/>
+      <c r="F22" s="191"/>
+      <c r="G22" s="71" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="19"/>
+      <c r="B23" s="20">
         <v>2</v>
       </c>
-      <c r="C23" s="135" t="s">
+      <c r="C23" s="162" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="163"/>
+      <c r="E23" s="163"/>
+      <c r="F23" s="164"/>
+      <c r="G23" s="65" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
+        <v>3</v>
+      </c>
+      <c r="C24" s="162" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="163"/>
+      <c r="E24" s="163"/>
+      <c r="F24" s="164"/>
+      <c r="G24" s="65" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="25"/>
+      <c r="B25" s="22">
+        <v>4</v>
+      </c>
+      <c r="C25" s="177"/>
+      <c r="D25" s="178"/>
+      <c r="E25" s="178"/>
+      <c r="F25" s="179"/>
+      <c r="G25" s="65"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="180" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="181"/>
+      <c r="E26" s="181"/>
+      <c r="F26" s="182"/>
+      <c r="G26" s="29"/>
+    </row>
+    <row r="27" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="30"/>
+      <c r="B27" s="20">
+        <v>4</v>
+      </c>
+      <c r="C27" s="159" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" s="160"/>
+      <c r="E27" s="160"/>
+      <c r="F27" s="161"/>
+      <c r="G27" s="65" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="30"/>
+      <c r="B28" s="20">
+        <v>5</v>
+      </c>
+      <c r="C28" s="159" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="160"/>
+      <c r="E28" s="160"/>
+      <c r="F28" s="161"/>
+      <c r="G28" s="65" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="31"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="183"/>
+      <c r="D29" s="184"/>
+      <c r="E29" s="184"/>
+      <c r="F29" s="185"/>
+      <c r="G29" s="28"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="18">
+        <v>1</v>
+      </c>
+      <c r="C30" s="186"/>
+      <c r="D30" s="187"/>
+      <c r="E30" s="187"/>
+      <c r="F30" s="188"/>
+      <c r="G30" s="29"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="33"/>
+      <c r="B31" s="20">
+        <v>2</v>
+      </c>
+      <c r="C31" s="171" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="172"/>
+      <c r="E31" s="172"/>
+      <c r="F31" s="173"/>
+      <c r="G31" s="66" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="33"/>
+      <c r="B32" s="20">
+        <v>3</v>
+      </c>
+      <c r="C32" s="153" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="154"/>
+      <c r="E32" s="154"/>
+      <c r="F32" s="155"/>
+      <c r="G32" s="66" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="34"/>
+      <c r="B33" s="48">
+        <v>4</v>
+      </c>
+      <c r="C33" s="174" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="175"/>
+      <c r="E33" s="175"/>
+      <c r="F33" s="176"/>
+      <c r="G33" s="70" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="55"/>
+      <c r="C34" s="116" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="136"/>
-      <c r="E23" s="136"/>
-      <c r="F23" s="137"/>
-    </row>
-    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
-        <v>3</v>
-      </c>
-      <c r="C24" s="135" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="136"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="137"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="24"/>
-      <c r="B25" s="21">
-        <v>4</v>
-      </c>
-      <c r="C25" s="147"/>
-      <c r="D25" s="148"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="149"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="150" t="s">
-        <v>39</v>
-      </c>
-      <c r="D26" s="151"/>
-      <c r="E26" s="151"/>
-      <c r="F26" s="152"/>
-    </row>
-    <row r="27" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="27"/>
-      <c r="B27" s="19">
-        <v>4</v>
-      </c>
-      <c r="C27" s="153" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="154"/>
-      <c r="E27" s="154"/>
-      <c r="F27" s="155"/>
-    </row>
-    <row r="28" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="27"/>
-      <c r="B28" s="19">
-        <v>5</v>
-      </c>
-      <c r="C28" s="153" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" s="154"/>
-      <c r="E28" s="154"/>
-      <c r="F28" s="155"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="28"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="156"/>
-      <c r="D29" s="157"/>
-      <c r="E29" s="157"/>
-      <c r="F29" s="158"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="17">
-        <v>1</v>
-      </c>
-      <c r="C30" s="159"/>
-      <c r="D30" s="160"/>
-      <c r="E30" s="160"/>
-      <c r="F30" s="161"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="30"/>
-      <c r="B31" s="19">
-        <v>2</v>
-      </c>
-      <c r="C31" s="138" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="140"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="30"/>
-      <c r="B32" s="19">
-        <v>3</v>
-      </c>
-      <c r="C32" s="141" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="142"/>
-      <c r="E32" s="142"/>
-      <c r="F32" s="143"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="31"/>
-      <c r="B33" s="45">
-        <v>4</v>
-      </c>
-      <c r="C33" s="144" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="145"/>
-      <c r="E33" s="145"/>
-      <c r="F33" s="146"/>
-    </row>
-    <row r="34" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="51"/>
-      <c r="C34" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="57"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D34" s="116"/>
+      <c r="E34" s="116"/>
+      <c r="F34" s="116"/>
+      <c r="G34" s="52"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
         <v>15</v>
       </c>
@@ -2862,7 +3100,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B36" s="1" t="s">
         <v>16</v>
       </c>
@@ -2872,20 +3110,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C18:F18"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C24:F24"/>
@@ -2901,6 +3125,20 @@
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2931,7 +3169,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" customWidth="1"/>
@@ -2940,10 +3178,11 @@
     <col min="4" max="4" width="17.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="18.140625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -2951,15 +3190,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -2967,7 +3206,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
@@ -2976,32 +3215,32 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="32"/>
+      <c r="C6" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="35"/>
       <c r="E6" s="10">
         <v>4</v>
       </c>
@@ -3009,343 +3248,404 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="107" t="s">
+    <row r="7" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="107"/>
-      <c r="E7" s="33" t="s">
-        <v>77</v>
+      <c r="D7" s="87"/>
+      <c r="E7" s="36" t="s">
+        <v>93</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+    </row>
+    <row r="9" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="103" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-    </row>
-    <row r="10" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+      <c r="C9" s="112" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+    </row>
+    <row r="10" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="37"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A11" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="17">
+      <c r="D10" s="38"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A11" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="18">
         <v>3</v>
       </c>
       <c r="C11" s="165" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D11" s="166"/>
       <c r="E11" s="166"/>
       <c r="F11" s="167"/>
-      <c r="L11" s="56"/>
-    </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19">
+      <c r="G11" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" s="60"/>
+    </row>
+    <row r="12" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="19"/>
+      <c r="B12" s="20">
         <v>4</v>
       </c>
-      <c r="C12" s="67" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="69"/>
-    </row>
-    <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19">
+      <c r="C12" s="123" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="66" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="19"/>
+      <c r="B13" s="20">
         <v>5</v>
       </c>
-      <c r="C13" s="67" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="69"/>
-    </row>
-    <row r="14" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19">
+      <c r="C13" s="123" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="124"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="66" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="19"/>
+      <c r="B14" s="20">
         <v>6</v>
       </c>
-      <c r="C14" s="180" t="s">
+      <c r="C14" s="204" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="205"/>
+      <c r="E14" s="205"/>
+      <c r="F14" s="206"/>
+      <c r="G14" s="70" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="24">
+        <v>2</v>
+      </c>
+      <c r="C15" s="207" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="208"/>
+      <c r="E15" s="208"/>
+      <c r="F15" s="209"/>
+      <c r="G15" s="69" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A16" s="19"/>
+      <c r="B16" s="20">
+        <v>3</v>
+      </c>
+      <c r="C16" s="123" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="124"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="65" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="19"/>
+      <c r="B17" s="20">
+        <v>4</v>
+      </c>
+      <c r="C17" s="153" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="154"/>
+      <c r="E17" s="154"/>
+      <c r="F17" s="155"/>
+      <c r="G17" s="66" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27">
+        <v>5</v>
+      </c>
+      <c r="C18" s="103"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="66"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="24">
+        <v>3</v>
+      </c>
+      <c r="C19" s="117" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="71" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="19"/>
+      <c r="B20" s="20">
+        <v>4</v>
+      </c>
+      <c r="C20" s="123" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="181"/>
-      <c r="E14" s="181"/>
-      <c r="F14" s="182"/>
-    </row>
-    <row r="15" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="23">
+    </row>
+    <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="19"/>
+      <c r="B21" s="20">
+        <v>5</v>
+      </c>
+      <c r="C21" s="123" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="66" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="25"/>
+      <c r="B22" s="22">
+        <v>6</v>
+      </c>
+      <c r="C22" s="103" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="104"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="66" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="24">
         <v>2</v>
       </c>
-      <c r="C15" s="183" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="184"/>
-      <c r="E15" s="184"/>
-      <c r="F15" s="185"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19">
+      <c r="C23" s="213" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="214"/>
+      <c r="E23" s="214"/>
+      <c r="F23" s="215"/>
+      <c r="G23" s="74" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="19"/>
+      <c r="B24" s="20">
         <v>3</v>
       </c>
-      <c r="C16" s="67" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="69"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19">
+      <c r="C24" s="153" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="154"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="155"/>
+      <c r="G24" s="66" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="19"/>
+      <c r="B25" s="20">
         <v>4</v>
       </c>
-      <c r="C17" s="141" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="142"/>
-      <c r="E17" s="142"/>
-      <c r="F17" s="143"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26">
+      <c r="C25" s="153" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="154"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="155"/>
+      <c r="G25" s="65" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="25"/>
+      <c r="B26" s="22">
         <v>5</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="66"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="23">
+      <c r="C26" s="210" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="211"/>
+      <c r="E26" s="211"/>
+      <c r="F26" s="212"/>
+      <c r="G26" s="68" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="24">
+        <v>2</v>
+      </c>
+      <c r="C27" s="78" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="79"/>
+      <c r="E27" s="79"/>
+      <c r="F27" s="80"/>
+      <c r="G27" s="71" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="30"/>
+      <c r="B28" s="20">
         <v>3</v>
       </c>
-      <c r="C19" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="60"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19">
+      <c r="C28" s="153" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="154"/>
+      <c r="E28" s="154"/>
+      <c r="F28" s="155"/>
+      <c r="G28" s="72" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="30"/>
+      <c r="B29" s="20">
         <v>4</v>
       </c>
-      <c r="C20" s="67" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="69"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19">
+      <c r="C29" s="201"/>
+      <c r="D29" s="202"/>
+      <c r="E29" s="202"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="65"/>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="31"/>
+      <c r="B30" s="22">
         <v>5</v>
       </c>
-      <c r="C21" s="67" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="69"/>
-    </row>
-    <row r="22" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="24"/>
-      <c r="B22" s="21">
-        <v>6</v>
-      </c>
-      <c r="C22" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="66"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="23">
+      <c r="C30" s="198"/>
+      <c r="D30" s="199"/>
+      <c r="E30" s="199"/>
+      <c r="F30" s="200"/>
+      <c r="G30" s="63"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="18">
+        <v>1</v>
+      </c>
+      <c r="C31" s="192" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="193"/>
+      <c r="E31" s="193"/>
+      <c r="F31" s="194"/>
+      <c r="G31" s="29"/>
+    </row>
+    <row r="32" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="33"/>
+      <c r="B32" s="20">
         <v>2</v>
       </c>
-      <c r="C23" s="177" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="178"/>
-      <c r="E23" s="178"/>
-      <c r="F23" s="179"/>
-    </row>
-    <row r="24" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19">
+      <c r="C32" s="123"/>
+      <c r="D32" s="124"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="125"/>
+      <c r="G32" s="66"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="34"/>
+      <c r="B33" s="48">
         <v>3</v>
       </c>
-      <c r="C24" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="142"/>
-      <c r="E24" s="142"/>
-      <c r="F24" s="143"/>
-    </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19">
-        <v>4</v>
-      </c>
-      <c r="C25" s="141" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="142"/>
-      <c r="E25" s="142"/>
-      <c r="F25" s="143"/>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="24"/>
-      <c r="B26" s="21">
-        <v>5</v>
-      </c>
-      <c r="C26" s="174" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="175"/>
-      <c r="E26" s="175"/>
-      <c r="F26" s="176"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="23">
-        <v>2</v>
-      </c>
-      <c r="C27" s="123" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="124"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="125"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="27"/>
-      <c r="B28" s="19">
-        <v>3</v>
-      </c>
-      <c r="C28" s="141" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="142"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="143"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="27"/>
-      <c r="B29" s="19">
-        <v>4</v>
-      </c>
-      <c r="C29" s="195"/>
-      <c r="D29" s="196"/>
-      <c r="E29" s="196"/>
-      <c r="F29" s="197"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="28"/>
-      <c r="B30" s="21">
-        <v>5</v>
-      </c>
-      <c r="C30" s="192"/>
-      <c r="D30" s="193"/>
-      <c r="E30" s="193"/>
-      <c r="F30" s="194"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="17">
-        <v>1</v>
-      </c>
-      <c r="C31" s="186" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" s="187"/>
-      <c r="E31" s="187"/>
-      <c r="F31" s="188"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="30"/>
-      <c r="B32" s="19">
-        <v>2</v>
-      </c>
-      <c r="C32" s="67"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="68"/>
-      <c r="F32" s="69"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="31"/>
-      <c r="B33" s="45">
-        <v>3</v>
-      </c>
-      <c r="C33" s="189"/>
-      <c r="D33" s="190"/>
-      <c r="E33" s="190"/>
-      <c r="F33" s="191"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="46"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="195"/>
+      <c r="D33" s="196"/>
+      <c r="E33" s="196"/>
+      <c r="F33" s="197"/>
+      <c r="G33" s="28"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="49"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
         <v>15</v>
       </c>
@@ -3353,7 +3653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B36" s="1" t="s">
         <v>16</v>
       </c>
@@ -3363,22 +3663,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C26:F26"/>
@@ -3388,6 +3672,22 @@
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
